--- a/accor/data/eval_sim_v1_old_vs_new.xlsx
+++ b/accor/data/eval_sim_v1_old_vs_new.xlsx
@@ -491,25 +491,25 @@
         <v>3289.56</v>
       </c>
       <c r="E2" t="n">
-        <v>3289.56</v>
+        <v>3127.368383068118</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-162.19</v>
       </c>
       <c r="G2" t="n">
         <v>3172.96</v>
       </c>
       <c r="H2" t="n">
-        <v>3172.96</v>
+        <v>3122.62597692836</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-50.33</v>
       </c>
       <c r="J2" t="n">
         <v>156.2</v>
       </c>
       <c r="K2" t="n">
-        <v>156.2</v>
+        <v>141.6761113763683</v>
       </c>
     </row>
     <row r="3">
@@ -528,25 +528,25 @@
         <v>1280.32</v>
       </c>
       <c r="E3" t="n">
-        <v>1280.32</v>
+        <v>1201.367709334711</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-78.95</v>
       </c>
       <c r="G3" t="n">
         <v>898.0700000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>898.0700000000001</v>
+        <v>873.5627481327078</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-24.51</v>
       </c>
       <c r="J3" t="n">
         <v>243.1</v>
       </c>
       <c r="K3" t="n">
-        <v>243.1</v>
+        <v>225.1893764348243</v>
       </c>
     </row>
     <row r="4">
@@ -565,25 +565,25 @@
         <v>1450.46</v>
       </c>
       <c r="E4" t="n">
-        <v>1450.46</v>
+        <v>1042.840930421113</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-407.62</v>
       </c>
       <c r="G4" t="n">
         <v>1310.73</v>
       </c>
       <c r="H4" t="n">
-        <v>1310.73</v>
+        <v>1184.232283858011</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-126.5</v>
       </c>
       <c r="J4" t="n">
         <v>95.8</v>
       </c>
       <c r="K4" t="n">
-        <v>95.8</v>
+        <v>70.03815342548089</v>
       </c>
     </row>
     <row r="5">
@@ -602,16 +602,16 @@
         <v>7137.9</v>
       </c>
       <c r="E5" t="n">
-        <v>7137.9</v>
+        <v>7137.896509448529</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G5" t="n">
         <v>7310.08</v>
       </c>
       <c r="H5" t="n">
-        <v>7310.08</v>
+        <v>7310.082898794361</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -620,7 +620,7 @@
         <v>129.8</v>
       </c>
       <c r="K5" t="n">
-        <v>129.8</v>
+        <v>129.8008042687997</v>
       </c>
     </row>
   </sheetData>
@@ -762,22 +762,18 @@
         <v>28</v>
       </c>
       <c r="K2" t="n">
-        <v>13763.77</v>
+        <v>13763.77397182734</v>
       </c>
       <c r="L2" t="n">
-        <v>9638</v>
+        <v>9638.00397182734</v>
       </c>
       <c r="M2" t="n">
-        <v>8089.26</v>
+        <v>8089.263722709286</v>
       </c>
       <c r="N2" t="n">
-        <v>8067.97</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>H3546</t>
-        </is>
-      </c>
+        <v>8067.973722709286</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0</v>
       </c>
@@ -823,27 +819,23 @@
         <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>2291.58</v>
+        <v>2133.673743264406</v>
       </c>
       <c r="L3" t="n">
-        <v>1851.87</v>
+        <v>1693.963743264406</v>
       </c>
       <c r="M3" t="n">
-        <v>1362.03</v>
+        <v>1313.029995855019</v>
       </c>
       <c r="N3" t="n">
-        <v>1527.88</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>HB6A3</t>
-        </is>
-      </c>
+        <v>1478.879995855019</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-157.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-49</v>
       </c>
     </row>
     <row r="4">
@@ -884,24 +876,20 @@
         <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>13202.17</v>
+        <v>13202.17095293028</v>
       </c>
       <c r="L4" t="n">
-        <v>4637.79</v>
+        <v>4637.789047069718</v>
       </c>
       <c r="M4" t="n">
-        <v>7948.47</v>
+        <v>7948.472074879434</v>
       </c>
       <c r="N4" t="n">
-        <v>6552.19</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>H0373</t>
-        </is>
-      </c>
+        <v>6552.192074879435</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -945,22 +933,18 @@
         <v>21</v>
       </c>
       <c r="K5" t="n">
-        <v>795.83</v>
+        <v>795.8292544112999</v>
       </c>
       <c r="L5" t="n">
-        <v>329.22</v>
+        <v>329.2207455887001</v>
       </c>
       <c r="M5" t="n">
-        <v>537.22</v>
+        <v>537.2238814061591</v>
       </c>
       <c r="N5" t="n">
-        <v>435.89</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>HB5I0</t>
-        </is>
-      </c>
+        <v>435.8938814061591</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
@@ -1006,27 +990,23 @@
         <v>26</v>
       </c>
       <c r="K6" t="n">
-        <v>4156.76</v>
+        <v>3341.521115253527</v>
       </c>
       <c r="L6" t="n">
-        <v>2571.7</v>
+        <v>1756.461115253527</v>
       </c>
       <c r="M6" t="n">
-        <v>2309.33</v>
+        <v>2056.320686309863</v>
       </c>
       <c r="N6" t="n">
-        <v>2185.58</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>H6188</t>
-        </is>
-      </c>
+        <v>1932.570686309863</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-815.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-253.01</v>
       </c>
     </row>
     <row r="7">
@@ -1067,27 +1047,23 @@
         <v>19</v>
       </c>
       <c r="K7" t="n">
-        <v>379.42</v>
+        <v>379.4183245949843</v>
       </c>
       <c r="L7" t="n">
-        <v>708.77</v>
+        <v>708.7716754050157</v>
       </c>
       <c r="M7" t="n">
-        <v>226.73</v>
+        <v>226.7255004103966</v>
       </c>
       <c r="N7" t="n">
-        <v>268.25</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>H2075</t>
-        </is>
-      </c>
+        <v>268.2455004103966</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -1136,10 +1112,10 @@
         <v>3289.56</v>
       </c>
       <c r="C2" t="n">
-        <v>3289.56</v>
+        <v>3127.368383068118</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-162.19</v>
       </c>
     </row>
     <row r="3">
@@ -1152,10 +1128,10 @@
         <v>3172.96</v>
       </c>
       <c r="C3" t="n">
-        <v>3172.96</v>
+        <v>3122.62597692836</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-50.33</v>
       </c>
     </row>
   </sheetData>
